--- a/docs/ops/my-project-capability-architecture.xlsx
+++ b/docs/ops/my-project-capability-architecture.xlsx
@@ -1,38 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="能力架构" sheetId="1" r:id="rId1"/>
-    <sheet name="状态统计" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="能力架构" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="状态统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'能力架构'!$A$1:$E$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'状态统计'!$A$1:$C$6</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
-      <sz val="11"/>
       <name val="Aptos"/>
       <family val="2"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="Aptos"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="6">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -75,745 +81,1133 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="20"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="54" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">能力域</t>
+          <t>能力域</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">子能力</t>
+          <t>子能力</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">状态</t>
+          <t>状态</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">你现在的实际能力</t>
+          <t>你现在的实际能力</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">代码依据</t>
+          <t>代码依据</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">设计工作台</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">无限画布与节点编辑</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>设计工作台</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>无限画布与节点编辑</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">已实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">有 canvas 工作区，支持文本、链接、分组等节点编辑与布局</t>
+          <t>有 canvas 工作区，支持文本、链接、分组、项目、文件等节点编辑与布局，文本节点可自动聚焦输入并按内容自动长高</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">workspace.html:88-95；scripts/workspace-page.js</t>
+          <t>workspace.html:95-103,148-159；scripts/workspace-page.js:892-1030,1554-1574；scripts/shared/workspace-board.js:25-33,168-178；tests/verify-workspace-text-edit.mjs</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">设计工作台</t>
-        </is>
-      </c>
-      <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">连线、框选、缩放、拖拽</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>设计工作台</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>连线、框选、缩放、拖拽</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">已实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">支持节点连线、框选、多种交互、视图缩放与移动</t>
+          <t>支持悬停显示连线端点、自动选择连线落边、框选、多节点拖拽、视图缩放与移动</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">workspace.html:98-102；scripts/workspace-page.js</t>
+          <t>scripts/workspace-page.js:817-832,892-914,2179-2242；tests/verify-workspace-edge-connect.mjs:93-207</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">设计工作台</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Undo/Redo、导入导出、复制粘贴</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>设计工作台</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Undo/Redo、导入导出、复制粘贴</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">已实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">有历史回退、导入导出、复制粘贴、重置视图等编辑控制</t>
+          <t>有历史回退、导入导出、复制粘贴、重置视图等编辑控制</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">workspace.html:92-95；scripts/workspace-page.js:1500-1755</t>
+          <t>workspace.html:92-95；scripts/workspace-page.js:1500-1755</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">实时协同</t>
-        </is>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">服务端快照持久化</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>设计工作台</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>图片/PDF 附件上传与文件节点</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">已实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">有 /api/boards/:boardId，支持 board 读写与持久化</t>
+          <t>可在画布中通过 File 入口或拖拽插入图片/PDF，本地上传后生成 file 节点并直接预览</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">server.mjs:573-586；tests/verify-board-snapshots-api.mjs</t>
+          <t>workspace.html:95-103,154-159；server.mjs:644-695,768-770；scripts/workspace-page.js:980-1028,1884-1961,2466-2495；tests/verify-workspace-file-node-ui.mjs:106-235；tests/verify-workspace-file-upload-api.mjs</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">实时协同</t>
-        </is>
-      </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WebSocket 实时同步</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>实时协同</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>服务端快照持久化</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">已实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">已接入 Yjs + WebSocket 的多人实时同步链路</t>
+          <t>有 /api/boards/:boardId，支持 board 读写与持久化</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">realtime-collaboration-server.mjs:50-118</t>
+          <t>server.mjs:573-586；tests/verify-board-snapshots-api.mjs</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">实时协同</t>
-        </is>
-      </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Presence 感知</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>实时协同</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>WebSocket 实时同步</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">已实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">已有远端光标、远端选区、远端编辑态显示</t>
+          <t>已接入 Yjs + WebSocket 的多人实时同步链路</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">workspace.html:101；tests/verify-realtime-collaboration-ui.mjs:99-217</t>
+          <t>realtime-collaboration-server.mjs:50-118</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AI协同设计</t>
-        </is>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">画布上下文感知</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>实时协同</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Presence 感知</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">已实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI 会带上 selected / nearby / connected / visible nodes 一起理解</t>
+          <t>已有远端光标、远端选区、远端编辑态显示</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts/workspace-page.js:1608-1646</t>
+          <t>workspace.html:101；tests/verify-realtime-collaboration-ui.mjs:99-217</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AI协同设计</t>
-        </is>
-      </c>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AI 回答并改板</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI协同设计</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>画布上下文感知</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">已实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">/api/workspace-assistant 会返回 operations 并直接改 board</t>
+          <t>AI 会带上 selected / nearby / connected / visible nodes 一起理解</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts/workspace-page.js:1668-1699；server.mjs:420-470</t>
+          <t>scripts/workspace-page.js:1608-1646</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AI协同设计</t>
-        </is>
-      </c>
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">多轮会话上下文</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">部分实现</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI协同设计</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>AI 回答并改板</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>已实现</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">当前页面内有消息线程和上下文延续，但不是跨项目、跨会话长期记忆</t>
+          <t>/api/workspace-assistant 会返回 operations 并直接改 board</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts/workspace-page.js:1654-1665</t>
+          <t>scripts/workspace-page.js:1668-1699；server.mjs:420-470</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">项目数据层</t>
-        </is>
-      </c>
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">项目台账</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已实现</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AI协同设计</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>多轮会话上下文</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>部分实现</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">有 Project Ledger，包含项目、客户、状态、预算、负责人、团队</t>
+          <t>当前页面内有消息线程和上下文延续，但不是跨项目、跨会话长期记忆</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">projects.html:61-89；scripts/projects-page.js</t>
+          <t>scripts/workspace-page.js:1654-1665</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">项目数据层</t>
-        </is>
-      </c>
-      <c r="B12" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">项目到画布联动</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>项目数据层</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>项目台账</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">已实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">可以从项目页直接跳转到对应 project canvas</t>
+          <t>有 Project Ledger，包含项目、客户、状态、预算、负责人、团队</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts/projects-page.js:74-90；scripts/workspace-page.js:1212-1232</t>
+          <t>projects.html:61-89；scripts/projects-page.js</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">项目数据层</t>
-        </is>
-      </c>
-      <c r="B13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">项目知识沉淀</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">部分实现</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>项目数据层</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>项目到画布联动</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>已实现</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">已有项目结构化数据和 board snapshot，但还不是完整知识库/知识图谱</t>
+          <t>可以从项目页直接跳转到对应 project canvas</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts/shared/studio-data-client.js:129-209；server.mjs:573-586</t>
+          <t>scripts/projects-page.js:74-90；scripts/workspace-page.js:1212-1232</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">资产数据层</t>
-        </is>
-      </c>
-      <c r="B14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">资产库展示</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已实现</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>项目数据层</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>项目知识沉淀</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>部分实现</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">有 Digital Assets 页面和资产网格</t>
+          <t>已有项目结构化数据和 board snapshot，但还不是完整知识库/知识图谱</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets.html:61-90；scripts/assets-page.js:64-103</t>
+          <t>scripts/shared/studio-data-client.js:129-209；server.mjs:573-586</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">资产数据层</t>
-        </is>
-      </c>
-      <c r="B15" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">搜索与分类筛选</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>资产数据层</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>资产库展示</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">已实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">支持 search 和 category filter</t>
+          <t>有 Digital Assets 页面和资产网格</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets.html:78-87；scripts/assets-page.js:64-83,212-222</t>
+          <t>assets.html:61-90；scripts/assets-page.js:64-103</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">资产数据层</t>
-        </is>
-      </c>
-      <c r="B16" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">资产问答</t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>资产数据层</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>搜索与分类筛选</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">已实现</t>
+          <t>已实现</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">资产页已有 AI assistant，可问项目、地点、交付物等</t>
+          <t>支持 search 和 category filter</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">assets.html:93-120；scripts/assets-page.js:148-196</t>
+          <t>assets.html:78-87；scripts/assets-page.js:64-83,212-222</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">资产数据层</t>
-        </is>
-      </c>
-      <c r="B17" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">自动打标与自动归类</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">未实现</t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>资产数据层</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>资产问答</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>已实现</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">现在还是人工结构化展示，不是自动标签系统</t>
+          <t>资产页已有 AI assistant，可问项目、地点、交付物等</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">当前代码库未见自动 tagging / classification 流程</t>
+          <t>assets.html:93-120；scripts/assets-page.js:148-196</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">智能理解层</t>
-        </is>
-      </c>
-      <c r="B18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">图片识别/视觉理解</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>资产数据层</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>自动打标与自动归类</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">未实现</t>
+          <t>未实现</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">还没有 image understanding、识别、抽取、归类链路</t>
+          <t>现在还是人工结构化展示，不是自动标签系统</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">当前代码库未见视觉识别链路</t>
+          <t>当前代码库未见自动 tagging / classification 流程</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">智能理解层</t>
-        </is>
-      </c>
-      <c r="B19" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">多步骤流程编排</t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>智能理解层</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>图片识别/视觉理解</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">未实现</t>
+          <t>未实现</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">现在更像单轮助手，不是 workflow engine / agent orchestration</t>
+          <t>还没有 image understanding、识别、抽取、归类链路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">当前代码库未见流程编排引擎</t>
+          <t>当前代码库未见视觉识别链路</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">平台治理层</t>
-        </is>
-      </c>
-      <c r="B20" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">成员/角色/权限/邀请</t>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>智能理解层</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>多步骤流程编排</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">未实现</t>
+          <t>未实现</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">还没有 workspace member、RBAC、invite 这类团队治理能力</t>
+          <t>现在更像单轮助手，不是 workflow engine / agent orchestration</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">docs/plans/2026-03-28-realtime-collaboration-cloud-design.md:24-45</t>
+          <t>当前代码库未见流程编排引擎</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">平台治理层</t>
-        </is>
-      </c>
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">评论/批注/@通知</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>平台治理层</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>成员/角色/权限/邀请</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">未实现</t>
+          <t>未实现</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">还没有评论流、批注、mentions、notifications</t>
+          <t>还没有 workspace member、RBAC、invite 这类团队治理能力</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">docs/plans/2026-03-28-realtime-collaboration-cloud-design.md:116</t>
+          <t>docs/plans/2026-03-28-realtime-collaboration-cloud-design.md:24-45</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">平台治理层</t>
-        </is>
-      </c>
-      <c r="B22" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">计费/配额/租户治理</t>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>平台治理层</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>评论/批注/@通知</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">未实现</t>
+          <t>未实现</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">还没有 billing、quota、tenant 这一层平台能力</t>
+          <t>还没有评论流、批注、mentions、notifications</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">docs/plans/2026-03-28-realtime-collaboration-cloud-design.md:117</t>
+          <t>docs/plans/2026-03-28-realtime-collaboration-cloud-design.md:116</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>平台治理层</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>计费/配额/租户治理</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>未实现</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>还没有 billing、quota、tenant 这一层平台能力</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>docs/plans/2026-03-28-realtime-collaboration-cloud-design.md:117</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E22"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">指标</t>
+          <t>指标</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">值</t>
+          <t>值</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明</t>
+          <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">总能力项</t>
-        </is>
-      </c>
-      <c r="B2" s="0">
-        <v>21</v>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">当前这版能力架构共统计的子能力数量</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>总能力项</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>当前这版能力架构共统计的子能力数量</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已实现</t>
-        </is>
-      </c>
-      <c r="B3" s="0">
-        <v>13</v>
-      </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">代码和测试中已经能确认可用</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>已实现</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>代码和测试中已经能确认可用</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">部分实现</t>
-        </is>
-      </c>
-      <c r="B4" s="0">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>部分实现</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">已有入口或局部闭环，但不足以算完整产品能力</t>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>已有入口或局部闭环，但不足以算完整产品能力</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">未实现</t>
-        </is>
-      </c>
-      <c r="B5" s="0">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>未实现</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">当前代码库中未见产品化实现</t>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>当前代码库中未见产品化实现</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">判定口径</t>
-        </is>
-      </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">当前代码库</t>
-        </is>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">依据现有前端页面、服务端接口、协同服务与测试脚本判断</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>判定口径</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>当前代码库</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>依据现有前端页面、服务端接口、协同服务与测试脚本判断</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>